--- a/output.xlsx
+++ b/output.xlsx
@@ -462,31 +462,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>803818</v>
+        <v>803819</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>宗人府供事</t>
+          <t>都督府別駕</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Clerk in the Imperial Clan Court</t>
+          <t>Administrator of the Commander-in-chief\'s Office</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>zong ren fu gong shi</t>
+          <t>du du fu bie jia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>24844</t>
         </is>
       </c>
     </row>
